--- a/reports/jobs_2026-10-01.xlsx
+++ b/reports/jobs_2026-10-01.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Power and Performance Engineer, PAI Platforms and Performance Analysis</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -538,131 +538,127 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.arm.com/job/san-jose/power-and-performance-engineer-pai-platforms-and-performance-analysis/33099/77390277488</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.arm.com/</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Arm India</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>GPU Hardware Verification Engineer</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.arm.com/job/cambridge/gpu-hardware-verification-engineer/33099/92118503728</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.arm.com/</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Arm India</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Verification Engineer - Media IP</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4739199005</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.arm.com/job/bengaluru/verification-engineer-media-ip/33099/101393917664</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.arm.com/</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Agnikul Cosmos</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Careers Inquiries humancapital@agnikul.in</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>mailto:%20humancapital@agnikul.in</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>https://agnikul.in/careers</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Agoda India</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Chiang Mai 1 available jobs</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 0 available jobs Ok</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/location/chiang-mai/</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Agnikul Cosmos</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Dubai 0 available jobs</t>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -675,11 +671,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 0 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -687,12 +679,12 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/dubai/</t>
+          <t>mailto:%20humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://agnikul.in/careers</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -709,7 +701,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 0 available jobs</t>
+          <t>Chiang Mai 1 available jobs</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -734,7 +726,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai/</t>
+          <t>https://careersatagoda.com/location/chiang-mai/</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -756,7 +748,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Shanghai 1 available jobs</t>
+          <t>Dubai 0 available jobs</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -781,7 +773,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/shanghai/</t>
+          <t>https://careersatagoda.com/location/dubai/</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -803,7 +795,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Technology</t>
+          <t>Mumbai 0 available jobs</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -816,7 +808,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -824,7 +820,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/department/technology/</t>
+          <t>https://careersatagoda.com/location/mumbai/</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -846,7 +842,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Key Takeaways from Agoda’s AI Developer Report 2026 September 29, 2026 /</t>
+          <t>Shanghai 1 available jobs</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -859,7 +855,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -867,7 +867,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-agodas-ai-developer-report-2026/</t>
+          <t>https://careersatagoda.com/location/shanghai/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>How Agoda is evolving engineering support with AI agents September 22, 2026 /</t>
+          <t>Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/how-agoda-is-evolving-engineering-support-with-ai-agents/</t>
+          <t>https://careersatagoda.com/department/technology/</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Mumbai jobs</t>
+          <t>Key Takeaways from Agoda’s AI Developer Report 2026 September 29, 2026 /</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -945,11 +945,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai jobs Yokohama jobs</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -957,7 +953,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai-india/</t>
+          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-agodas-ai-developer-report-2026/</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -979,12 +975,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer Jobs</t>
+          <t>How Agoda is evolving engineering support with AI agents September 22, 2026 /</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1000,7 +996,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
+          <t>https://careersatagoda.com/blog/tech/how-agoda-is-evolving-engineering-support-with-ai-agents/</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1022,12 +1018,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer Jobs</t>
+          <t>Mumbai jobs</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1035,7 +1031,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai jobs Yokohama jobs</t>
+        </is>
+      </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
+          <t>https://careersatagoda.com/location/mumbai-india/</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Jobs</t>
+          <t>Backend Developer Jobs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
+          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1103,17 +1103,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Atlan</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Field Security Engineer</t>
+          <t>Full Stack Developer Jobs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1121,11 +1121,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -1133,12 +1129,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
+          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1150,12 +1146,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Software Engineer Jobs</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1176,12 +1172,12 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
+          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1198,12 +1194,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AI and Machine Learning</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1219,7 +1215,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1236,17 +1232,17 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Product Launch and price new features without waiting on engineering</t>
+          <t>AI and Machine Learning</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1262,12 +1258,12 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/product/</t>
+          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1284,7 +1280,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Growth Test offers, run promotions and lift conversion</t>
+          <t>Product Launch and price new features without waiting on engineering</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1305,7 +1301,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/growth/</t>
+          <t>https://www.chargebee.com/solutions/role/product/</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1322,17 +1318,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Databricks India</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+          <t>Growth Test offers, run promotions and lift conversion</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1340,11 +1336,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Remote - India</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -1352,12 +1344,12 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
+          <t>https://www.chargebee.com/solutions/role/growth/</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/databricks</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1374,7 +1366,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer, FDE (Forward Deployed Engineer)</t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1389,7 +1381,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, India; Delhi, India; Mumbai, India; Pune, India</t>
+          <t>Remote - India</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1399,7 +1391,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8015848002</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1416,17 +1408,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Databricks India</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>AI Engineer, FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1436,7 +1428,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru, India; Delhi, India; Mumbai, India; Pune, India</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1446,12 +1438,12 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8015848002</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://boards.greenhouse.io/databricks</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1468,12 +1460,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1483,7 +1475,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1493,7 +1485,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1515,12 +1507,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-3</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1530,7 +1522,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1540,7 +1532,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1562,7 +1554,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Integration &amp; Customisation Engineer-3</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1577,7 +1569,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1587,7 +1579,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1609,12 +1601,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1622,7 +1614,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>India Full-time</t>
+        </is>
+      </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -1630,7 +1626,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1652,12 +1648,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1665,11 +1661,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -1677,7 +1669,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1699,7 +1691,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1724,7 +1716,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1746,7 +1738,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Forward Deployed Engineer - 3</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1771,7 +1763,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1793,12 +1785,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Golang/Java/Python)</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1818,7 +1810,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1840,12 +1832,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Software Developer - 3 (Golang/Java/Python)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1865,7 +1857,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1887,12 +1879,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1912,7 +1904,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1929,17 +1921,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1949,7 +1941,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1959,12 +1951,12 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -1976,17 +1968,17 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Engineering Leader, Google COE</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1994,7 +1986,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -2002,12 +1998,12 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2019,12 +2015,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Engineering Leader, Google COE</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2045,12 +2041,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2062,17 +2058,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2088,12 +2084,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2110,12 +2106,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2131,7 +2127,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2148,17 +2144,17 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2166,11 +2162,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru-VTP, India</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -2178,12 +2170,12 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2200,7 +2192,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2225,7 +2217,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2242,17 +2234,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2262,7 +2254,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2272,12 +2264,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2289,17 +2281,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer (Java / .NET)</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2309,7 +2301,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, in</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2319,12 +2311,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000152347660</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2341,12 +2333,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Backend Engineer (Java / .NET)</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2356,7 +2348,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Bangalore, in</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2366,7 +2358,7 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000152347660</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -2383,17 +2375,17 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2403,7 +2395,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2413,12 +2405,12 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2430,17 +2422,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2448,7 +2440,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -2456,12 +2452,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2478,12 +2474,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2499,7 +2495,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -2516,12 +2512,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2534,11 +2530,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>Chennai, Tamil Nadu</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -2546,12 +2538,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2568,7 +2560,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2583,7 +2575,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2593,7 +2585,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -2610,12 +2602,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2628,7 +2620,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -2636,12 +2632,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2653,12 +2649,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2671,11 +2667,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
       <c r="F49" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -2683,12 +2675,12 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2700,17 +2692,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2718,7 +2710,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -2726,12 +2722,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2743,17 +2739,17 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2769,12 +2765,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2786,12 +2782,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2804,11 +2800,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
       <c r="F52" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -2816,12 +2808,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2838,7 +2830,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2853,7 +2845,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2863,7 +2855,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -2885,7 +2877,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2900,7 +2892,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2910,7 +2902,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -2932,7 +2924,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Noida</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2947,7 +2939,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2957,7 +2949,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -2974,17 +2966,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Talent Acquisition Intern - Noida</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2992,7 +2984,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -3000,12 +2996,12 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -3017,17 +3013,17 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3035,11 +3031,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
       <c r="F57" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -3047,12 +3039,12 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3069,12 +3061,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3094,7 +3086,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3116,12 +3108,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3141,7 +3133,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3158,17 +3150,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3176,7 +3168,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -3184,12 +3180,12 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3201,12 +3197,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3219,11 +3215,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
       <c r="F61" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -3231,12 +3223,12 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3253,12 +3245,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3268,7 +3260,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -3278,7 +3270,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -3300,12 +3292,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (CPD) - Winter Intern</t>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3315,7 +3307,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -3325,7 +3317,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3347,12 +3339,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Software Engineer (CPD) - Winter Intern</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3362,7 +3354,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -3372,7 +3364,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -3394,12 +3386,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Winter Intern</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3409,7 +3401,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -3419,7 +3411,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -3436,17 +3428,17 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Software Engineer - Winter Intern</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3456,7 +3448,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Remote Instructor- Python</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3466,12 +3458,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3483,17 +3475,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Video Editor- AI</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3501,7 +3493,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Remote Instructor- Python</t>
+        </is>
+      </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -3509,12 +3505,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3531,7 +3527,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Sound Designer - AI</t>
+          <t>AI Screenplay Writer</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3552,7 +3548,7 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -3574,7 +3570,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>Video Editor- AI</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3595,7 +3591,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -3612,17 +3608,17 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Sound Designer - AI</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3630,11 +3626,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -3642,12 +3634,12 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -3659,17 +3651,17 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3677,11 +3669,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -3689,12 +3677,12 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3706,17 +3694,17 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>SirionLabs</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3724,7 +3712,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -3732,12 +3724,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://www.sirion.ai/jobs/integration-support-engineer/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://www.sirionlabs.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3749,17 +3741,17 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>SirionLabs</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure Transformation Engineer – IT</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3767,7 +3759,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -3775,12 +3771,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://www.sirion.ai/jobs/infrastructure-transformation-engineer-it/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://www.sirionlabs.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3792,17 +3788,17 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3818,12 +3814,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://www.sirion.ai/jobs/integration-support-engineer/</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3835,17 +3831,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Infrastructure Transformation Engineer – IT</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3853,11 +3849,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
       <c r="F75" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -3865,12 +3857,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://www.sirion.ai/jobs/infrastructure-transformation-engineer-it/</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3882,12 +3874,12 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Thoughtworks India</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Developer (Vapasi) - Intern</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -3897,14 +3889,10 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>1–5 years</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, India</t>
-        </is>
-      </c>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr"/>
       <c r="F76" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -3912,12 +3900,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8210384?gh_jid=8210384</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/thoughtworks</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3929,17 +3917,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3949,7 +3937,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -3959,12 +3947,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -3976,52 +3964,146 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
+          <t>Thoughtworks India</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Developer (Vapasi) - Intern</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>1–5 years</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, India</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thoughtworks.com/careers/jobs/8210384?gh_jid=8210384</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/thoughtworks</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
           <t>Unacademy</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Test Jerin</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>Software Engineer, Backend</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t>Bengaluru, in</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
         <is>
           <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr">
         <is>
           <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
-      <c r="I78" s="4" t="inlineStr">
+      <c r="I80" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I78"/>
+  <autoFilter ref="A1:I80"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4100,6 +4182,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId79"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4111,7 +4195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4159,15 +4243,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Keka</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.keka.com/careers</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.keka.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Log9 Materials</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4176,18 +4280,38 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Krutrim</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.olakrutrim.com/careers</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.olakrutrim.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4196,18 +4320,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Vymo</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://getvymo.com/careers/</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4216,18 +4340,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4236,18 +4360,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Blinkit</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://blinkit.com/careers</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4256,18 +4380,38 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capillary Technologies</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.capillarytech.com/careers/</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.capillarytech.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4276,38 +4420,58 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Capillary Technologies</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://www.capillarytech.com/careers/</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Nykaa</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.nykaa.com/careers</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
+Call log:
+  - navigating to "https://www.nykaa.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Juspay</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://juspay.io/careers</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
-  - navigating to "https://www.capillarytech.com/careers/", waiting until "networkidle"
+  - navigating to "https://juspay.io/careers", waiting until "networkidle"
 </t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Darwinbox</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://darwinbox.com/careers</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4316,58 +4480,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Nykaa</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://www.nykaa.com/careers</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
-Call log:
-  - navigating to "https://www.nykaa.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Juspay</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://juspay.io/careers</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://juspay.io/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4376,18 +4500,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>FirstCry</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://www.firstcry.com/careers</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4396,38 +4520,58 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>OYO</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://www.oyorooms.com/careers/</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PharmEasy</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://pharmeasy.in/careers</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
-  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
+  - navigating to "https://pharmeasy.in/careers", waiting until "networkidle"
 </t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Pocket FM</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://pocketfm.com/careers</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://pocketfm.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -4436,18 +4580,38 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Shiprocket</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://www.shiprocket.in/careers/</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.shiprocket.in/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4456,18 +4620,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4476,18 +4640,38 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>upGrad</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.upgrad.com/careers/</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.upgrad.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
